--- a/sample-data/purchase_register.xlsx
+++ b/sample-data/purchase_register.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaitali\OneDrive\Desktop\k\gstmatch-frontend\sample-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ed99a3060035074b/Desktop/k/gstmatch-frontend/sample-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B200A47D-3288-4874-B60B-4704D5BD71EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B200A47D-3288-4874-B60B-4704D5BD71EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40AB90C9-E3A6-4196-8250-97E0FC1B9A7E}"/>
   <bookViews>
-    <workbookView xWindow="1416" yWindow="1848" windowWidth="21624" windowHeight="11112" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase Register" sheetId="1" r:id="rId1"/>
@@ -404,6 +404,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
